--- a/spec/greyborn-tuning.xlsx
+++ b/spec/greyborn-tuning.xlsx
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="912">
   <si>
     <t xml:space="preserve">Greyborn — Tuning Spreadsheet</t>
   </si>
@@ -2618,6 +2618,33 @@
   </si>
   <si>
     <t xml:space="preserve">Fortress ally reduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aggression Power bonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version B §5 / gdd 31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aggression Speed bonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aggression kill core bonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tactical Control bonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tactical Health bonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tactical capture speedup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulwark ally reduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec 02 Titan Tactical L10</t>
   </si>
   <si>
     <t xml:space="preserve">Tension rates and event decks (Spec 05 §8)</t>
@@ -13915,7 +13942,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36"/>
@@ -15550,7 +15577,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
         <v>837</v>
       </c>
@@ -15564,7 +15591,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
         <v>839</v>
       </c>
@@ -15578,7 +15605,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
         <v>840</v>
       </c>
@@ -15592,7 +15619,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
         <v>841</v>
       </c>
@@ -15606,7 +15633,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
         <v>842</v>
       </c>
@@ -15620,7 +15647,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
         <v>843</v>
       </c>
@@ -15634,7 +15661,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
         <v>844</v>
       </c>
@@ -15648,7 +15675,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
         <v>846</v>
       </c>
@@ -15662,7 +15689,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
         <v>847</v>
       </c>
@@ -15676,7 +15703,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
         <v>848</v>
       </c>
@@ -15690,7 +15717,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
         <v>849</v>
       </c>
@@ -15704,7 +15731,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
         <v>850</v>
       </c>
@@ -15718,7 +15745,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
         <v>851</v>
       </c>
@@ -15732,7 +15759,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
         <v>852</v>
       </c>
@@ -15746,7 +15773,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
         <v>854</v>
       </c>
@@ -15760,7 +15787,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
         <v>855</v>
       </c>
@@ -15772,6 +15799,104 @@
       </c>
       <c r="D89" s="3" t="s">
         <v>853</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>864</v>
       </c>
     </row>
   </sheetData>
@@ -15802,7 +15927,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>856</v>
+        <v>865</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -15818,7 +15943,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>857</v>
+        <v>866</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>705</v>
@@ -15831,91 +15956,91 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>858</v>
+        <v>867</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>0.2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>859</v>
+        <v>868</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>860</v>
+        <v>869</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>859</v>
+        <v>868</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>861</v>
+        <v>870</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>1.5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>862</v>
+        <v>871</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>863</v>
+        <v>872</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>862</v>
+        <v>871</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>864</v>
+        <v>873</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>865</v>
+        <v>874</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>866</v>
+        <v>875</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>-0.5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>859</v>
+        <v>868</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>100</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>868</v>
+        <v>877</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -15929,7 +16054,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>869</v>
+        <v>878</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -15938,7 +16063,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>870</v>
+        <v>879</v>
       </c>
       <c r="B13" s="3" t="n">
         <f aca="false">B4+B5*10/60</f>
@@ -15950,7 +16075,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>871</v>
+        <v>880</v>
       </c>
       <c r="B14" s="3" t="n">
         <f aca="false">ROUND(B10/B13,0)</f>
@@ -15962,7 +16087,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>872</v>
+        <v>881</v>
       </c>
       <c r="B15" s="3" t="n">
         <f aca="false">ROUND(B14/60,1)</f>
@@ -15981,16 +16106,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>873</v>
+        <v>882</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>874</v>
+        <v>883</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>875</v>
+        <v>884</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>876</v>
+        <v>885</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>111</v>
@@ -15998,10 +16123,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>877</v>
+        <v>886</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>878</v>
+        <v>887</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>0.25</v>
@@ -16010,15 +16135,15 @@
         <v>30</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>877</v>
+        <v>886</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>880</v>
+        <v>889</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>0.2</v>
@@ -16027,15 +16152,15 @@
         <v>20</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>881</v>
+        <v>890</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>877</v>
+        <v>886</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>882</v>
+        <v>891</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>0.2</v>
@@ -16044,15 +16169,15 @@
         <v>30</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>883</v>
+        <v>892</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>877</v>
+        <v>886</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>884</v>
+        <v>893</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>0.2</v>
@@ -16061,15 +16186,15 @@
         <v>30</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>885</v>
+        <v>894</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>877</v>
+        <v>886</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>886</v>
+        <v>895</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>0.15</v>
@@ -16078,15 +16203,15 @@
         <v>30</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>887</v>
+        <v>896</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>0.4</v>
@@ -16095,15 +16220,15 @@
         <v>20</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>891</v>
+        <v>900</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>0.4</v>
@@ -16112,15 +16237,15 @@
         <v>15</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>892</v>
+        <v>901</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>893</v>
+        <v>902</v>
       </c>
       <c r="C25" s="13" t="n">
         <v>0.2</v>
@@ -16129,15 +16254,15 @@
         <v>45</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>894</v>
+        <v>903</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>895</v>
+        <v>904</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>896</v>
+        <v>905</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>0.4</v>
@@ -16146,15 +16271,15 @@
         <v>15</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>897</v>
+        <v>906</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>895</v>
+        <v>904</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>898</v>
+        <v>907</v>
       </c>
       <c r="C27" s="13" t="n">
         <v>0.4</v>
@@ -16163,15 +16288,15 @@
         <v>10</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>899</v>
+        <v>908</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>895</v>
+        <v>904</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>900</v>
+        <v>909</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>0.2</v>
@@ -16180,7 +16305,7 @@
         <v>45</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>901</v>
+        <v>910</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16192,7 +16317,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>902</v>
+        <v>911</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -16201,7 +16326,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>877</v>
+        <v>886</v>
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="12" t="n">
@@ -16213,7 +16338,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="12" t="n">
@@ -16225,7 +16350,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>895</v>
+        <v>904</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="12" t="n">
